--- a/importaciones_productos/HAP11350 registro productos.xlsx
+++ b/importaciones_productos/HAP11350 registro productos.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>22101</v>
+        <v>221.01</v>
       </c>
     </row>
   </sheetData>

--- a/importaciones_productos/HAP11350 registro productos.xlsx
+++ b/importaciones_productos/HAP11350 registro productos.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>BOLSEGBLAUn</t>
+          <t>SEGBLAPORUn</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
